--- a/docs/公众号内容盘点表.xlsx
+++ b/docs/公众号内容盘点表.xlsx
@@ -1274,8 +1274,16 @@
           <t>heyi-suihuajili</t>
         </is>
       </c>
-      <c r="D26" s="21" t="inlineStr"/>
-      <c r="E26" s="21" t="inlineStr"/>
+      <c r="D26" s="21" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>网站骨架已建（7篇占位），待填充正文</t>
+        </is>
+      </c>
       <c r="F26" s="21" t="inlineStr"/>
       <c r="G26" s="21" t="inlineStr">
         <is>

--- a/docs/公众号内容盘点表.xlsx
+++ b/docs/公众号内容盘点表.xlsx
@@ -1281,7 +1281,7 @@
       </c>
       <c r="E26" s="21" t="inlineStr">
         <is>
-          <t>网站骨架已建（7篇占位），待填充正文</t>
+          <t>已迁移7篇正文（公众号链接直抓），待 Push 上线</t>
         </is>
       </c>
       <c r="F26" s="21" t="inlineStr"/>
